--- a/artfynd/A 61670-2025 artfynd.xlsx
+++ b/artfynd/A 61670-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105159879</v>
+        <v>105159881</v>
       </c>
       <c r="B2" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>602958.5320156998</v>
+        <v>602981</v>
       </c>
       <c r="R2" t="n">
-        <v>7029419.661140265</v>
+        <v>7029425</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105159895</v>
+        <v>105159888</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>602977.3340536759</v>
+        <v>603022</v>
       </c>
       <c r="R3" t="n">
-        <v>7029449.886420557</v>
+        <v>7029357</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +844,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105159891</v>
+        <v>105159889</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603065.8341976268</v>
+        <v>603014</v>
       </c>
       <c r="R4" t="n">
-        <v>7029339.185718074</v>
+        <v>7029352</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -980,19 +945,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105159890</v>
+        <v>105159892</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1039,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603033.5959302064</v>
+        <v>603085</v>
       </c>
       <c r="R5" t="n">
-        <v>7029335.455489851</v>
+        <v>7029363</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,19 +1046,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1139,15 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>105159881</v>
+        <v>105159894</v>
       </c>
       <c r="B6" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1155,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1179,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>602980.8350563539</v>
+        <v>603079</v>
       </c>
       <c r="R6" t="n">
-        <v>7029424.866271154</v>
+        <v>7029379</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1212,19 +1147,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105159880</v>
+        <v>105159879</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1295,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>602966.7139194391</v>
+        <v>602959</v>
       </c>
       <c r="R7" t="n">
-        <v>7029416.782590738</v>
+        <v>7029419</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1328,19 +1248,9 @@
           <t>2022-09-21</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-09-21</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,6 +1274,718 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>105159880</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>602967</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7029417</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>105159887</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>603024</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7029367</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>105159890</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>603034</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7029336</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>105159891</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>603066</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7029339</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>105159893</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>603075</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7029367</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>105159895</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>602978</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7029450</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>105159886</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Norrtannflo värdetrakt, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>603024</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7029367</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Resele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2022-09-21</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Upplog, två honor</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
         <is>
           <t>Naturvärdesinventering Y-län</t>
         </is>

--- a/artfynd/A 61670-2025 artfynd.xlsx
+++ b/artfynd/A 61670-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105159881</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105159888</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105159889</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105159892</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105159894</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105159879</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105159880</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105159887</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105159890</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105159891</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105159893</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105159895</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,8 +2055,28 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105159886</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>